--- a/docs/analisis-requisitos/HU-CPA-4650-PARTE-PUBLICA-CATEGORIAS-CPA-CPA-VIRTUAL_V0.xlsx
+++ b/docs/analisis-requisitos/HU-CPA-4650-PARTE-PUBLICA-CATEGORIAS-CPA-CPA-VIRTUAL_V0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_CPA_Virtual\HU\SP2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_CPA_Virtual\HU\SP7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB72176-67E8-4737-8A67-EB8918B2836A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8742422-E82E-4719-B431-A460387E8096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="204" xr2:uid="{611E275B-AF68-4D54-8B4F-28D93EBAB353}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="50">
   <si>
     <t>Enunciado de la historia</t>
   </si>
@@ -86,9 +86,6 @@
     <t>Se presenta en el formulario el botón Volver</t>
   </si>
   <si>
-    <t>Cabecera</t>
-  </si>
-  <si>
     <t>Filtros búsqueda</t>
   </si>
   <si>
@@ -129,6 +126,9 @@
   </si>
   <si>
     <t xml:space="preserve">Formulario Categorías CPA Parte Pública </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cada una de las categorías de (talleres, actividades o servicios), presentará una tipo categoría, nombre, descripción, color, imagen </t>
   </si>
   <si>
     <t xml:space="preserve">Si el tipo de categoría seleccionado es 'Taller', se pasará al formulario detallado en la HU-CPA-4680-PARTE-PUBLICA-TALLERES-CPA-CPA-VIRTUAL).
@@ -149,89 +149,8 @@
     <t>Permitirá salir del presente formulario y volver al Formulario Acceso Parte Pública (HU-CPA-4500-ACCESO-PARTE-PUBLICA-CPA-CPA-VIRTUAL)</t>
   </si>
   <si>
-    <t>Si se selecciona una categoría del listado y se decide pulsar.</t>
-  </si>
-  <si>
-    <t>Campo texto. No editable. En función de que el acceso a la pantalla sea desde 'Talleres', 'Actividades' o 'Servicios' el valor por defecto será 'Talleres' ,  'Actividades' o 'Servicios', según corresponda.</t>
-  </si>
-  <si>
-    <t>Botón Aplicar</t>
-  </si>
-  <si>
-    <t>Se presenta en el formulario el botón Aplicar</t>
-  </si>
-  <si>
-    <t>Filtro Código Postal</t>
-  </si>
-  <si>
-    <t>Campo numérico. Editable. No obligatorio.</t>
-  </si>
-  <si>
-    <t>Se mostrará el valor introducido en pantalla.</t>
-  </si>
-  <si>
-    <t>Filtro Almería</t>
-  </si>
-  <si>
-    <t>Campo check. Editable. No obligatorio.</t>
-  </si>
-  <si>
-    <t>Filtro Cádiz</t>
-  </si>
-  <si>
-    <t>Filtro Córdoba</t>
-  </si>
-  <si>
-    <t>Filtro Granada</t>
-  </si>
-  <si>
-    <t>Filtro Huelva</t>
-  </si>
-  <si>
-    <t>Filtro Jaen</t>
-  </si>
-  <si>
-    <t>Filtro Málaga</t>
-  </si>
-  <si>
-    <t>Filtro Sevilla</t>
-  </si>
-  <si>
-    <t>Se mostrará el valor obtenido previamente.</t>
-  </si>
-  <si>
-    <t>Campo color. No editable</t>
-  </si>
-  <si>
-    <t>Campo multimedia. No editable</t>
-  </si>
-  <si>
-    <t>Cada una de las categorías de (talleres, actividades o servicios), presentará una tipo categoría, nombre, descripción, color, imagen, estado</t>
-  </si>
-  <si>
-    <t>Listado Temáticas</t>
-  </si>
-  <si>
-    <t>tipo Temática</t>
-  </si>
-  <si>
-    <t>nombre Temática</t>
-  </si>
-  <si>
-    <t>descripcion Temática</t>
-  </si>
-  <si>
-    <t>color Temática</t>
-  </si>
-  <si>
-    <t>Imagen Temática</t>
-  </si>
-  <si>
-    <t>estado Temática</t>
-  </si>
-  <si>
     <r>
-      <t>Mediante la operación '</t>
+      <t>Se presenta en pantalla el valor obtenido mediante la operación '</t>
     </r>
     <r>
       <rPr>
@@ -241,7 +160,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>ConsultaResultadoListadoCategorias</t>
+      <t>consultarDefinicionCategoría</t>
     </r>
     <r>
       <rPr>
@@ -249,34 +168,17 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>' que accederá a los tipos de contenido 'Temáticas', 'EstadosTemáticas' se obtendrá una relación de todos aquellas Categorías (de Talleres, Actividades o Servicios), coincidentes con los criterios definidos en los filtros de búsqueda.</t>
+      <t>'.</t>
     </r>
   </si>
   <si>
-    <t>Filtro Tipo Temática</t>
-  </si>
-  <si>
-    <t>Detalle Temática</t>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">Se presentará información relacionada con las categorías de talleres, actividades o servicios definidas para la categoría y CPA previamente seleccionados.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Mediante la operación '</t>
+      <t>Se presentará información relacionada con las categorías de talleres, actividades o servicios definidas para la categoría y CPA previamente seleccionados.
+Mediante la operación '</t>
     </r>
     <r>
       <rPr>
         <b/>
-        <strike/>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
@@ -286,47 +188,110 @@
     </r>
     <r>
       <rPr>
-        <strike/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>' que accederá al tipo de contenido 'Conceptos' del repositorio Drupal, se presentará en pantalla la imagen y definición de lo que se entiende por categoría de taller, actividad o servicio.</t>
+    </r>
+  </si>
+  <si>
+    <t>Si se selecciona una categoría del listado y se decide pulsar.</t>
+  </si>
+  <si>
+    <t>Campo texto. No editable. En función de que el acceso a la pantalla sea desde 'Talleres', 'Actividades' o 'Servicios' el valor por defecto será 'Talleres' ,  'Actividades' o 'Servicios', según corresponda.</t>
+  </si>
+  <si>
+    <t>Botón Aplicar</t>
+  </si>
+  <si>
+    <t>Se presenta en el formulario el botón Aplicar</t>
+  </si>
+  <si>
+    <t>Selección Centro</t>
+  </si>
+  <si>
+    <t>Listado Tematicas</t>
+  </si>
+  <si>
+    <r>
+      <t>Si el tipo de categoría seleccionado es 'Taller', mediante la operación '</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color indexed="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ConsultaListadoCategoriasTalleresCPA'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> que accederá a los tipos de contenido 'Tematicas', 'TalleresCentro' y 'Centros' se obtendrá una relación de todas aquellas Categorías de Talleres que tengan un Taller en el CPA previamente seleccionado.
+Si el tipo de categoría seleccionado es 'Actividad', mediante la operación '</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>' que accederá al tipo de contenido 'Conceptos' del repositorio Drupal, se presentará en pantalla la imagen y definición de lo que se entiende por categoría de taller, actividad o servicio.</t>
+      <t>ConsultaListadoCategoriasActividadesCPA</t>
     </r>
-  </si>
-  <si>
     <r>
-      <t>Se presenta en pantalla el valor obtenido mediante la operación '</t>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>' que accederá a los tipos de contenido 'Tematicas', 'ActividadesCentro' y 'Centros' se obtendrá una relación de todas aquellas Categorías de Actividades que tengan una actividad en el CPA previamente seleccionado.
+Si el tipo de categoría seleccionado es 'Servicio', mediante la operación '</t>
     </r>
     <r>
       <rPr>
         <b/>
-        <strike/>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>consultarDefinicionCategoría</t>
+      <t>ConsultaListadoServiciosCategoriaCPA</t>
     </r>
     <r>
       <rPr>
-        <strike/>
         <sz val="10"/>
-        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>'.</t>
+      <t>' que accederá a los tipos de contenido 'Tematicas', 'ServiciosCentro' y 'Centros' se obtendrá una relación de todas aquellos Categorías de Servicios que tengan un servicio en el CPA previamente seleccionado.</t>
     </r>
+  </si>
+  <si>
+    <t>Filtro Tipo Tematica</t>
+  </si>
+  <si>
+    <t>Detalle Tematica</t>
+  </si>
+  <si>
+    <t>Cabecera Tematica</t>
+  </si>
+  <si>
+    <t>Imagen Tematica</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -346,17 +311,9 @@
       <family val="2"/>
     </font>
     <font>
-      <strike/>
+      <b/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <strike/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color indexed="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -445,7 +402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -466,12 +423,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -498,20 +449,20 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1308382</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>120828</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>412892</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>146051</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagen 3">
+        <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{175C8949-CDD2-F118-AAC7-9D7A70981CE6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEF4A271-E28D-9F35-2171-99EA1E3BEAC7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -527,8 +478,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="5493032" cy="3454578"/>
+          <a:off x="0" y="1"/>
+          <a:ext cx="2768742" cy="3638550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>584200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>235113</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EB48B83-3123-FB2E-442C-F2218097E9B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2940050" y="44450"/>
+          <a:ext cx="3168813" cy="3543300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -895,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD33D8B-FAA8-4740-A39A-FB2519115401}">
-  <dimension ref="A24:I53"/>
+  <dimension ref="A24:I39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.7265625" customWidth="1"/>
@@ -954,22 +949,22 @@
     </row>
     <row r="26" spans="1:9" ht="125.5" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>29</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E26" s="2">
         <v>1</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>35</v>
@@ -978,7 +973,7 @@
         <v>12</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -988,7 +983,7 @@
       <c r="D27" s="7"/>
       <c r="E27" s="2"/>
       <c r="F27" s="3" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
@@ -1003,10 +998,10 @@
         <v>2</v>
       </c>
       <c r="F28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>12</v>
@@ -1024,10 +1019,10 @@
         <v>3</v>
       </c>
       <c r="F29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>12</v>
@@ -1045,10 +1040,10 @@
         <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>12</v>
@@ -1066,10 +1061,10 @@
         <v>5</v>
       </c>
       <c r="F31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>12</v>
@@ -1078,455 +1073,165 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="38" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
-      <c r="E32" s="8">
-        <v>6</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>68</v>
-      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
     </row>
     <row r="33" spans="1:9" ht="38" x14ac:dyDescent="0.25">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
-      <c r="E33" s="8">
-        <v>7</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="9" t="s">
+      <c r="E33" s="2">
+        <v>6</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I33" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I33" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="38" x14ac:dyDescent="0.25">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
-      <c r="E34" s="2"/>
+      <c r="E34" s="2">
+        <v>7</v>
+      </c>
       <c r="F34" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-    </row>
-    <row r="35" spans="1:9" ht="87.5" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
-      <c r="E35" s="2">
-        <v>6</v>
-      </c>
+      <c r="E35" s="2"/>
       <c r="F35" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="25" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" spans="1:9" ht="87.5" x14ac:dyDescent="0.25">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="25" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="301.5" x14ac:dyDescent="0.25">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G37" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H37" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:9" ht="162.5" x14ac:dyDescent="0.25">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="25" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="50" x14ac:dyDescent="0.25">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="25" x14ac:dyDescent="0.25">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="2">
-        <v>11</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="25" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="2">
-        <v>12</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="25" x14ac:dyDescent="0.25">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="2">
-        <v>13</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="25" x14ac:dyDescent="0.25">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="2">
-        <v>14</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="25" x14ac:dyDescent="0.25">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="2">
-        <v>15</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="88" x14ac:dyDescent="0.25">
-      <c r="A45" s="7"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="2">
-        <v>16</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="162.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="7"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="2">
-        <v>17</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="7"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="7"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="7"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="7"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="7"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="50" x14ac:dyDescent="0.25">
-      <c r="A53" s="7"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="2">
-        <v>18</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I53" s="3" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="4">
-    <mergeCell ref="A26:A53"/>
-    <mergeCell ref="B26:B53"/>
-    <mergeCell ref="C26:C53"/>
-    <mergeCell ref="D26:D53"/>
+    <mergeCell ref="A26:A39"/>
+    <mergeCell ref="B26:B39"/>
+    <mergeCell ref="C26:C39"/>
+    <mergeCell ref="D26:D39"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
